--- a/test_cases.xlsx
+++ b/test_cases.xlsx
@@ -30,7 +30,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -40,11 +40,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="004472C4"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFFF00"/>
       </patternFill>
     </fill>
   </fills>
@@ -60,15 +55,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -437,7 +429,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:J6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
@@ -525,31 +517,11 @@
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr"/>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>Call connects</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>(dry-run)</t>
-        </is>
-      </c>
-      <c r="H2" s="3" t="inlineStr">
-        <is>
-          <t>SKIP</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>Dry-run mode</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-04 03:21:27</t>
-        </is>
-      </c>
+      <c r="F2" s="2" t="inlineStr"/>
+      <c r="G2" s="2" t="inlineStr"/>
+      <c r="H2" s="2" t="inlineStr"/>
+      <c r="I2" s="2" t="inlineStr"/>
+      <c r="J2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -564,7 +536,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Phone2</t>
+          <t>Phone1</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -577,31 +549,11 @@
           <t>Hello world</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>SMS composer opens</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>(dry-run)</t>
-        </is>
-      </c>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>SKIP</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>Dry-run mode</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-04 03:21:27</t>
-        </is>
-      </c>
+      <c r="F3" s="2" t="inlineStr"/>
+      <c r="G3" s="2" t="inlineStr"/>
+      <c r="H3" s="2" t="inlineStr"/>
+      <c r="I3" s="2" t="inlineStr"/>
+      <c r="J3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -625,31 +577,11 @@
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr"/>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>USSD dialog appears</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>(dry-run)</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>SKIP</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>Dry-run mode</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-04 03:21:27</t>
-        </is>
-      </c>
+      <c r="F4" s="2" t="inlineStr"/>
+      <c r="G4" s="2" t="inlineStr"/>
+      <c r="H4" s="2" t="inlineStr"/>
+      <c r="I4" s="2" t="inlineStr"/>
+      <c r="J4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -677,31 +609,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>Setting changed</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>(dry-run)</t>
-        </is>
-      </c>
-      <c r="H5" s="3" t="inlineStr">
-        <is>
-          <t>SKIP</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>Dry-run mode</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-04 03:21:27</t>
-        </is>
-      </c>
+      <c r="F5" s="2" t="inlineStr"/>
+      <c r="G5" s="2" t="inlineStr"/>
+      <c r="H5" s="2" t="inlineStr"/>
+      <c r="I5" s="2" t="inlineStr"/>
+      <c r="J5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -727,29 +639,13 @@
       <c r="E6" s="2" t="inlineStr"/>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Returns '1'</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>(dry-run)</t>
-        </is>
-      </c>
-      <c r="H6" s="3" t="inlineStr">
-        <is>
-          <t>SKIP</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>Dry-run mode</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-04 03:21:27</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="inlineStr"/>
+      <c r="I6" s="2" t="inlineStr"/>
+      <c r="J6" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/test_cases.xlsx
+++ b/test_cases.xlsx
@@ -2,15 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="TestCases" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -26,11 +25,13 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -39,12 +40,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="004472C4"/>
+        <fgColor rgb="FF4472C4"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFFF00"/>
+        <fgColor rgb="FFFF0000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FF0000"/>
       </patternFill>
     </fill>
   </fills>
@@ -60,7 +66,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -68,12 +74,18 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -442,10 +454,8 @@
     <col width="6" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="30" customWidth="1" min="6" max="6"/>
-    <col width="30" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="4" max="5"/>
+    <col width="30" customWidth="1" min="6" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="30" customWidth="1" min="9" max="9"/>
     <col width="20" customWidth="1" min="10" max="10"/>
@@ -519,12 +529,12 @@
           <t>Phone1</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>+97699001122</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr"/>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>+97699920089</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="n"/>
       <c r="F2" s="2" t="inlineStr">
         <is>
           <t>Call connects</t>
@@ -532,22 +542,22 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>(dry-run)</t>
-        </is>
-      </c>
-      <c r="H2" s="3" t="inlineStr">
-        <is>
-          <t>SKIP</t>
+          <t>Starting: Intent { act=android.intent.action.CALL dat=tel:xxxxxxxxxxxx }</t>
+        </is>
+      </c>
+      <c r="H2" s="5" t="inlineStr">
+        <is>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>Dry-run mode</t>
+          <t>Starting: Intent { act=android.intent.action.CALL dat=tel:xxxxxxxxxxxx }</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-04 03:21:27</t>
+          <t>2026-06-04 11:52:05</t>
         </is>
       </c>
     </row>
@@ -564,17 +574,17 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Phone2</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>+97699001122</t>
+          <t>Phone1</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>+97699920089</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Hello world</t>
+          <t>Test</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -584,22 +594,22 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>(dry-run)</t>
-        </is>
-      </c>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>SKIP</t>
+          <t>Starting: Intent { act=android.intent.action.SENDTO dat=smsto:xxxxxxxxxxxx (has extras) }</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>Dry-run mode</t>
+          <t>Starting: Intent { act=android.intent.action.SENDTO dat=smsto:xxxxxxxxxxxx (has extras) }</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>2026-06-04 03:21:27</t>
+          <t>2026-06-04 11:49:38</t>
         </is>
       </c>
     </row>
@@ -624,7 +634,7 @@
           <t>*100#</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr"/>
+      <c r="E4" s="2" t="n"/>
       <c r="F4" s="2" t="inlineStr">
         <is>
           <t>USSD dialog appears</t>
@@ -632,22 +642,24 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>(dry-run)</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>SKIP</t>
+          <t>Starting: Intent { act=android.intent.action.DIAL dat=tel:xxxxx }
+Warning: Activity not started, its current task has been brought to the front</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>Dry-run mode</t>
+          <t>Starting: Intent { act=android.intent.action.DIAL dat=tel:xxxxx }
+Warning: Activity not started, its current task has been brought to the front</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>2026-06-04 03:21:27</t>
+          <t>2026-06-04 11:49:38</t>
         </is>
       </c>
     </row>
@@ -682,24 +694,16 @@
           <t>Setting changed</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>(dry-run)</t>
-        </is>
-      </c>
-      <c r="H5" s="3" t="inlineStr">
-        <is>
-          <t>SKIP</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>Dry-run mode</t>
-        </is>
-      </c>
+      <c r="G5" s="2" t="n"/>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="n"/>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2026-06-04 03:21:27</t>
+          <t>2026-06-04 11:49:39</t>
         </is>
       </c>
     </row>
@@ -724,7 +728,7 @@
           <t>global/wifi_on</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr"/>
+      <c r="E6" s="2" t="n"/>
       <c r="F6" s="2" t="inlineStr">
         <is>
           <t>Returns '1'</t>
@@ -732,22 +736,22 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>(dry-run)</t>
-        </is>
-      </c>
-      <c r="H6" s="3" t="inlineStr">
-        <is>
-          <t>SKIP</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>Dry-run mode</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2026-06-04 03:21:27</t>
+          <t>2026-06-04 11:49:40</t>
         </is>
       </c>
     </row>
